--- a/Bibsam_tidskriftslistor/scifree_data_karger.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_karger.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_2B86626789D34CA49253071FEE85455713EB838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C272C38-6DC4-4A8B-9BC2-C9404F303D78}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA5E0C4-7CBF-4460-8B35-FF353FBDF554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="363">
   <si>
     <t>Open</t>
   </si>
@@ -697,21 +697,12 @@
     <t>1016-6262</t>
   </si>
   <si>
-    <t>2673-298X</t>
-  </si>
-  <si>
-    <t>Complex Psychiatry</t>
-  </si>
-  <si>
     <t>2673-3633</t>
   </si>
   <si>
     <t>Glomerular Diseases</t>
   </si>
   <si>
-    <t>CC-BY, CC-BY-NC</t>
-  </si>
-  <si>
     <t>2813-0073</t>
   </si>
   <si>
@@ -910,9 +901,6 @@
     <t>https://www.karger.com/CMR</t>
   </si>
   <si>
-    <t>https://www.karger.com/CXP</t>
-  </si>
-  <si>
     <t>https://www.karger.com/CGR</t>
   </si>
   <si>
@@ -1118,6 +1106,9 @@
   </si>
   <si>
     <t>https://www.karger.com/VIS</t>
+  </si>
+  <si>
+    <t>CC-BY</t>
   </si>
 </sst>
 </file>
@@ -1173,16 +1164,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B566C458-9C78-40E8-A910-D83220DE7826}" name="Table2" displayName="Table2" ref="A1:G94" totalsRowShown="0">
-  <autoFilter ref="A1:G94" xr:uid="{B566C458-9C78-40E8-A910-D83220DE7826}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C1EC1E8F-AA0D-4061-BF67-94C047AA994A}" name="Table1" displayName="Table1" ref="A1:G93" totalsRowShown="0">
+  <autoFilter ref="A1:G93" xr:uid="{C1EC1E8F-AA0D-4061-BF67-94C047AA994A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G93">
+    <sortCondition ref="D1:D93"/>
+  </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{4C76505C-4340-48AD-A513-CD317122D6F8}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{8D4CA471-9670-4400-A0FD-8A3EAF0BBA82}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{AC096159-F817-4E4C-B77F-45F76B72F347}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{A25F1EF9-58C5-4C49-A921-3D00736F074A}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{E4F4D599-BD4C-40D4-A847-A8F4B0F55B1F}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{C4ECE40F-EDE4-4D59-B9B9-726A4BAFCBE2}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{606BBDDB-0A4A-479A-9E99-726C1F6F794F}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{B055E7CE-935B-41AE-9C87-07A928683D7E}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{42B57C34-F4E5-4FF0-A981-60CDCF0738F1}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{DC3FBB4B-1CAF-4458-A752-8758668BA9D6}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{8EABD15E-EBF4-4A61-AA39-24100FD08390}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{43290E6C-2671-4FC6-87D4-D6DA0AD1832B}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{A5DD3441-ABF1-44F8-8E5D-B477868F2F49}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{7FA43923-2C5E-4FA6-8026-C2680F90976A}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1450,15 +1444,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47498819-10B9-4F74-8D7C-237D05FC09EE}">
-  <dimension ref="A1:G94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F455B4A-D430-4299-B08B-230BD5F5EB21}">
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
   </cols>
@@ -1497,16 +1491,16 @@
         <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F2" t="s">
         <v>110</v>
       </c>
       <c r="G2" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1523,13 +1517,13 @@
         <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F3" t="s">
         <v>110</v>
       </c>
       <c r="G3" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1543,16 +1537,16 @@
         <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F4" t="s">
         <v>110</v>
       </c>
       <c r="G4" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1569,13 +1563,13 @@
         <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F5" t="s">
         <v>110</v>
       </c>
       <c r="G5" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1592,13 +1586,13 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F6" t="s">
         <v>110</v>
       </c>
       <c r="G6" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1612,13 +1606,13 @@
         <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1632,16 +1626,16 @@
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F8" t="s">
         <v>110</v>
       </c>
       <c r="G8" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1658,13 +1652,13 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F9" t="s">
         <v>110</v>
       </c>
       <c r="G9" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1681,13 +1675,13 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F10" t="s">
         <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1704,13 +1698,13 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
         <v>110</v>
       </c>
       <c r="G11" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1724,16 +1718,16 @@
         <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F12" t="s">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1750,13 +1744,13 @@
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F13" t="s">
         <v>110</v>
       </c>
       <c r="G13" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1770,13 +1764,13 @@
         <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F14" t="s">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1790,13 +1784,13 @@
         <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1810,13 +1804,13 @@
         <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F16" t="s">
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1830,13 +1824,13 @@
         <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1850,13 +1844,13 @@
         <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F18" t="s">
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1870,13 +1864,13 @@
         <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1890,16 +1884,16 @@
         <v>175</v>
       </c>
       <c r="D20" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E20" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F20" t="s">
         <v>110</v>
       </c>
       <c r="G20" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1916,13 +1910,13 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F21" t="s">
         <v>110</v>
       </c>
       <c r="G21" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1936,13 +1930,13 @@
         <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F22" t="s">
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1959,13 +1953,13 @@
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F23" t="s">
         <v>110</v>
       </c>
       <c r="G23" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1982,13 +1976,13 @@
         <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F24" t="s">
         <v>110</v>
       </c>
       <c r="G24" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1996,19 +1990,22 @@
         <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>225</v>
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>178</v>
       </c>
       <c r="D25" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E25" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F25" t="s">
         <v>110</v>
       </c>
       <c r="G25" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2016,22 +2013,22 @@
         <v>111</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D26" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E26" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F26" t="s">
         <v>110</v>
       </c>
       <c r="G26" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2039,22 +2036,19 @@
         <v>111</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="D27" t="s">
-        <v>238</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F27" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2062,19 +2056,22 @@
         <v>111</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
+        <v>180</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F28" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G28" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2082,22 +2079,22 @@
         <v>111</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F29" t="s">
         <v>110</v>
       </c>
       <c r="G29" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2105,22 +2102,22 @@
         <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>236</v>
       </c>
       <c r="E30" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F30" t="s">
         <v>110</v>
       </c>
       <c r="G30" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2128,22 +2125,22 @@
         <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D31" t="s">
-        <v>239</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F31" t="s">
         <v>110</v>
       </c>
       <c r="G31" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2151,22 +2148,22 @@
         <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>237</v>
       </c>
       <c r="E32" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F32" t="s">
         <v>110</v>
       </c>
       <c r="G32" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2174,22 +2171,19 @@
         <v>111</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="D33" t="s">
-        <v>240</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F33" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2197,19 +2191,19 @@
         <v>111</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>265</v>
       </c>
       <c r="E34" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F34" t="s">
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2217,19 +2211,22 @@
         <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>267</v>
+        <v>65</v>
+      </c>
+      <c r="C35" t="s">
+        <v>185</v>
       </c>
       <c r="D35" t="s">
-        <v>268</v>
+        <v>17</v>
       </c>
       <c r="E35" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F35" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G35" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2237,22 +2234,22 @@
         <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>238</v>
       </c>
       <c r="E36" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F36" t="s">
         <v>110</v>
       </c>
       <c r="G36" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2260,22 +2257,22 @@
         <v>111</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E37" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F37" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2283,22 +2280,22 @@
         <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D38" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E38" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F38" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G38" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2306,22 +2303,22 @@
         <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D39" t="s">
-        <v>243</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F39" t="s">
         <v>110</v>
       </c>
       <c r="G39" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2329,22 +2326,22 @@
         <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="C40" t="s">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="E40" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F40" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2352,22 +2349,22 @@
         <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="E41" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F41" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G41" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2375,22 +2372,19 @@
         <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="D42" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="E42" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F42" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2398,19 +2392,22 @@
         <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>227</v>
+        <v>71</v>
+      </c>
+      <c r="C43" t="s">
+        <v>191</v>
       </c>
       <c r="D43" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="E43" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F43" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G43" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2418,22 +2415,22 @@
         <v>111</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D44" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F44" t="s">
         <v>110</v>
       </c>
       <c r="G44" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2441,22 +2438,22 @@
         <v>111</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D45" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E45" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F45" t="s">
         <v>110</v>
       </c>
       <c r="G45" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2464,22 +2461,22 @@
         <v>111</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D46" t="s">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F46" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2487,22 +2484,19 @@
         <v>111</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F47" t="s">
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2510,19 +2504,22 @@
         <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>154</v>
+      </c>
+      <c r="C48" t="s">
+        <v>134</v>
       </c>
       <c r="D48" t="s">
-        <v>231</v>
+        <v>123</v>
       </c>
       <c r="E48" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F48" t="s">
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2530,22 +2527,22 @@
         <v>111</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="D49" t="s">
-        <v>123</v>
+        <v>245</v>
       </c>
       <c r="E49" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F49" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G49" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2553,22 +2550,22 @@
         <v>111</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D50" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E50" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F50" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2576,22 +2573,22 @@
         <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>249</v>
+        <v>124</v>
       </c>
       <c r="E51" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F51" t="s">
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2599,22 +2596,22 @@
         <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="D52" t="s">
-        <v>124</v>
+        <v>247</v>
       </c>
       <c r="E52" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F52" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G52" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2622,22 +2619,22 @@
         <v>111</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="C53" t="s">
-        <v>197</v>
+        <v>136</v>
       </c>
       <c r="D53" t="s">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="E53" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F53" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2645,22 +2642,22 @@
         <v>111</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E54" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F54" t="s">
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2668,22 +2665,22 @@
         <v>111</v>
       </c>
       <c r="B55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E55" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F55" t="s">
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2691,22 +2688,22 @@
         <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E56" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F56" t="s">
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2714,22 +2711,19 @@
         <v>111</v>
       </c>
       <c r="B57" t="s">
-        <v>159</v>
-      </c>
-      <c r="C57" t="s">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="D57" t="s">
-        <v>128</v>
+        <v>267</v>
       </c>
       <c r="E57" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F57" t="s">
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2737,19 +2731,19 @@
         <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>269</v>
+        <v>160</v>
       </c>
       <c r="D58" t="s">
-        <v>270</v>
+        <v>129</v>
       </c>
       <c r="E58" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F58" t="s">
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2757,19 +2751,22 @@
         <v>111</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="C59" t="s">
+        <v>140</v>
       </c>
       <c r="D59" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E59" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F59" t="s">
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -2777,22 +2774,22 @@
         <v>111</v>
       </c>
       <c r="B60" t="s">
-        <v>161</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="D60" t="s">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F60" t="s">
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -2800,22 +2797,22 @@
         <v>111</v>
       </c>
       <c r="B61" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="D61" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F61" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G61" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2823,22 +2820,22 @@
         <v>111</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D62" t="s">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="E62" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F62" t="s">
         <v>110</v>
       </c>
       <c r="G62" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -2846,22 +2843,22 @@
         <v>111</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D63" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E63" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F63" t="s">
         <v>110</v>
       </c>
       <c r="G63" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -2869,22 +2866,22 @@
         <v>111</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D64" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E64" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F64" t="s">
         <v>110</v>
       </c>
       <c r="G64" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -2892,22 +2889,22 @@
         <v>111</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C65" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D65" t="s">
-        <v>253</v>
+        <v>36</v>
       </c>
       <c r="E65" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F65" t="s">
         <v>110</v>
       </c>
       <c r="G65" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -2915,22 +2912,22 @@
         <v>111</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C66" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D66" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E66" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F66" t="s">
         <v>110</v>
       </c>
       <c r="G66" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -2938,22 +2935,22 @@
         <v>111</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D67" t="s">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="E67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F67" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -2961,22 +2958,22 @@
         <v>111</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D68" t="s">
-        <v>254</v>
+        <v>22</v>
       </c>
       <c r="E68" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F68" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G68" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -2984,22 +2981,22 @@
         <v>111</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="C69" t="s">
-        <v>205</v>
+        <v>141</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="E69" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F69" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3007,22 +3004,22 @@
         <v>111</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="C70" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="D70" t="s">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="E70" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F70" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G70" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3030,22 +3027,22 @@
         <v>111</v>
       </c>
       <c r="B71" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>206</v>
       </c>
       <c r="D71" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E71" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F71" t="s">
         <v>110</v>
       </c>
       <c r="G71" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3053,22 +3050,22 @@
         <v>111</v>
       </c>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C72" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D72" t="s">
-        <v>256</v>
+        <v>23</v>
       </c>
       <c r="E72" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F72" t="s">
         <v>110</v>
       </c>
       <c r="G72" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3076,22 +3073,22 @@
         <v>111</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F73" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3099,22 +3096,22 @@
         <v>111</v>
       </c>
       <c r="B74" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D74" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F74" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G74" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3122,22 +3119,22 @@
         <v>111</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
+        <v>254</v>
       </c>
       <c r="E75" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F75" t="s">
         <v>110</v>
       </c>
       <c r="G75" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3145,22 +3142,22 @@
         <v>111</v>
       </c>
       <c r="B76" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D76" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E76" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F76" t="s">
         <v>110</v>
       </c>
       <c r="G76" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3168,22 +3165,22 @@
         <v>111</v>
       </c>
       <c r="B77" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C77" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D77" t="s">
-        <v>258</v>
+        <v>26</v>
       </c>
       <c r="E77" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F77" t="s">
         <v>110</v>
       </c>
       <c r="G77" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3191,22 +3188,22 @@
         <v>111</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C78" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D78" t="s">
-        <v>26</v>
+        <v>256</v>
       </c>
       <c r="E78" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F78" t="s">
         <v>110</v>
       </c>
       <c r="G78" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3214,22 +3211,22 @@
         <v>111</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="C79" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
       <c r="D79" t="s">
-        <v>259</v>
+        <v>132</v>
       </c>
       <c r="E79" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F79" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3237,22 +3234,22 @@
         <v>111</v>
       </c>
       <c r="B80" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="C80" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="D80" t="s">
-        <v>132</v>
+        <v>257</v>
       </c>
       <c r="E80" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F80" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G80" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3260,22 +3257,22 @@
         <v>111</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C81" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D81" t="s">
-        <v>260</v>
+        <v>27</v>
       </c>
       <c r="E81" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F81" t="s">
         <v>110</v>
       </c>
       <c r="G81" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -3283,22 +3280,22 @@
         <v>111</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C82" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D82" t="s">
-        <v>27</v>
+        <v>258</v>
       </c>
       <c r="E82" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F82" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -3306,22 +3303,22 @@
         <v>111</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C83" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D83" t="s">
-        <v>261</v>
+        <v>28</v>
       </c>
       <c r="E83" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F83" t="s">
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3329,22 +3326,22 @@
         <v>111</v>
       </c>
       <c r="B84" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C84" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D84" t="s">
-        <v>28</v>
+        <v>259</v>
       </c>
       <c r="E84" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F84" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G84" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3352,22 +3349,19 @@
         <v>111</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
-      </c>
-      <c r="C85" t="s">
-        <v>218</v>
+        <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E85" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F85" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3375,19 +3369,22 @@
         <v>111</v>
       </c>
       <c r="B86" t="s">
-        <v>271</v>
+        <v>99</v>
+      </c>
+      <c r="C86" t="s">
+        <v>219</v>
       </c>
       <c r="D86" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="E86" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F86" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G86" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -3395,22 +3392,22 @@
         <v>111</v>
       </c>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="C87" t="s">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="D87" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E87" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F87" t="s">
         <v>110</v>
       </c>
       <c r="G87" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -3418,22 +3415,22 @@
         <v>111</v>
       </c>
       <c r="B88" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>108</v>
+        <v>220</v>
       </c>
       <c r="D88" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E88" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F88" t="s">
         <v>110</v>
       </c>
       <c r="G88" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -3441,22 +3438,22 @@
         <v>111</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C89" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D89" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E89" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F89" t="s">
         <v>110</v>
       </c>
       <c r="G89" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -3464,22 +3461,22 @@
         <v>111</v>
       </c>
       <c r="B90" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C90" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D90" t="s">
-        <v>266</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F90" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -3487,22 +3484,22 @@
         <v>111</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C91" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D91" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E91" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F91" t="s">
         <v>110</v>
       </c>
       <c r="G91" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -3510,22 +3507,22 @@
         <v>111</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D92" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F92" t="s">
         <v>110</v>
       </c>
       <c r="G92" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -3533,45 +3530,22 @@
         <v>111</v>
       </c>
       <c r="B93" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="C93" t="s">
-        <v>224</v>
+        <v>109</v>
       </c>
       <c r="D93" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E93" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F93" t="s">
         <v>110</v>
       </c>
       <c r="G93" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>111</v>
-      </c>
-      <c r="B94" t="s">
-        <v>43</v>
-      </c>
-      <c r="C94" t="s">
-        <v>109</v>
-      </c>
-      <c r="D94" t="s">
-        <v>31</v>
-      </c>
-      <c r="E94" t="s">
-        <v>365</v>
-      </c>
-      <c r="F94" t="s">
-        <v>110</v>
-      </c>
-      <c r="G94" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
